--- a/data/gebze/service_status_grid.xlsx
+++ b/data/gebze/service_status_grid.xlsx
@@ -1,45 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Desktop\bozankaya_ssh_takip\data\gebze\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4427D48F-D66D-4D72-8A6A-999A12F4AC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="4980" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Durum Tablosu" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Durum Tablosu" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="11">
+  <si>
+    <t>Tarih</t>
+  </si>
+  <si>
+    <t>✗</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>⚠</t>
+  </si>
+  <si>
+    <t>GDM1</t>
+  </si>
+  <si>
+    <t>GDM2</t>
+  </si>
+  <si>
+    <t>GDM3</t>
+  </si>
+  <si>
+    <t>GDM4</t>
+  </si>
+  <si>
+    <t>GDM5</t>
+  </si>
+  <si>
+    <t>GDM6</t>
+  </si>
+  <si>
+    <t>GDM7</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -64,14 +109,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,95 +133,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -464,595 +450,938 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D91"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H91"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tarih</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>G001</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>G002</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>G003</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>46013</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>46014</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>46015</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>46016</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>46017</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>46018</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>46019</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>46020</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>46021</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
         <v>46022</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>46023</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
         <v>46024</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
         <v>46025</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>46026</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>46027</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
         <v>46028</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <v>46029</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
         <v>46030</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
         <v>46031</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>46032</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
         <v>46033</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
         <v>46034</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
         <v>46035</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
         <v>46036</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
         <v>46037</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
         <v>46038</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
         <v>46039</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
         <v>46040</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
         <v>46041</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>46042</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>46043</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
         <v>46044</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
         <v>46045</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
         <v>46046</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
         <v>46047</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
         <v>46048</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
         <v>46049</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
         <v>46050</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
         <v>46051</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
         <v>46052</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
         <v>46053</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
         <v>46054</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
         <v>46055</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
         <v>46056</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
         <v>46057</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
         <v>46058</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
         <v>46059</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
         <v>46060</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
         <v>46061</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
         <v>46062</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
         <v>46063</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
         <v>46064</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
         <v>46065</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
         <v>46066</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
         <v>46067</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
         <v>46068</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
         <v>46069</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
         <v>46070</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
         <v>46071</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
         <v>46072</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
+    <row r="62" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
         <v>46073</v>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="B62" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
         <v>46074</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="B63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
         <v>46075</v>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="B64" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
         <v>46076</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="B65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
         <v>46077</v>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="B66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
         <v>46078</v>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="B67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
         <v>46079</v>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="B68" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
         <v>46080</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="B69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
         <v>46081</v>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="B70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
         <v>46082</v>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="B71" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
         <v>46083</v>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="B72" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
         <v>46084</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="B73" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
         <v>46085</v>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="B74" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
         <v>46086</v>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="B75" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
         <v>46087</v>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="B76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
         <v>46088</v>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="B77" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
         <v>46089</v>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="B78" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
         <v>46090</v>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="B79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
         <v>46091</v>
       </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="B80" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
         <v>46092</v>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="B81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
         <v>46093</v>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="B82" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
         <v>46094</v>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="B83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
         <v>46095</v>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="B84" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
         <v>46096</v>
       </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="B85" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
         <v>46097</v>
       </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="B86" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
         <v>46098</v>
       </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="B87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
         <v>46099</v>
       </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="B88" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
         <v>46100</v>
       </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="B89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
         <v>46101</v>
       </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="B90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
         <v>46102</v>
       </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
+      <c r="B91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
